--- a/src/test/resources/data/TestResults.xlsx
+++ b/src/test/resources/data/TestResults.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="25">
   <si>
     <t>STT</t>
   </si>
@@ -42,6 +42,51 @@
   </si>
   <si>
     <t>Mong đợi: đăng nhập thanh cong, chuyen den trang Dashboard | Thực tế: vẫn ở trang https://opensource-demo.orangehrmlive.com/web/index.php/auth/login</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Upload ảnh đại diện thành công</t>
+  </si>
+  <si>
+    <t>Cập nhật ảnh đại diện nhân viên</t>
+  </si>
+  <si>
+    <t>Mong đợi: kịch bản PASSED | thực tế: FAILED</t>
+  </si>
+  <si>
+    <t>PASSED</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Lọc người dùng theo username và role</t>
+  </si>
+  <si>
+    <t>Quan lý người dùng hệ thống</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Đăng nhập thất bại với mật khẩu sai</t>
+  </si>
+  <si>
+    <t>UNDEFINED</t>
+  </si>
+  <si>
+    <t>Mong đợi: kịch bản PASSED | thực tế: UNDEFINED</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Đăng nhập với nhiều bộ dữ liệu đọc từ file loginData.csv</t>
   </si>
 </sst>
 </file>
@@ -86,7 +131,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -113,14 +158,82 @@
       <c r="B2" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
-        <v>9</v>
+      <c r="E2" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/data/TestResults.xlsx
+++ b/src/test/resources/data/TestResults.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="25">
   <si>
     <t>STT</t>
   </si>
@@ -162,10 +162,10 @@
         <v>6</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -196,10 +196,10 @@
         <v>17</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -213,10 +213,10 @@
         <v>20</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">

--- a/src/test/resources/data/TestResults.xlsx
+++ b/src/test/resources/data/TestResults.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="25">
   <si>
     <t>STT</t>
   </si>
@@ -179,10 +179,10 @@
         <v>11</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
